--- a/tutorial_ninja_project/ExcelFiles/Book1.xlsx
+++ b/tutorial_ninja_project/ExcelFiles/Book1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Python_Selenium_Expleo\tutorial_ninja_project\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5258913D-DB9B-44E8-A007-E5B45F8E00C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{118E741D-4972-4E8E-823D-0ABF43E89149}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{DCA414FD-7B16-4848-8665-E653E9407BD6}"/>
   </bookViews>
